--- a/tabela_resumida.xlsx
+++ b/tabela_resumida.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="169">
   <si>
     <t>Nº</t>
   </si>
@@ -34,6 +34,483 @@
     <t>OM</t>
   </si>
   <si>
+    <t>Planejamento</t>
+  </si>
+  <si>
+    <t>Sessão Pública</t>
+  </si>
+  <si>
+    <t>Concluído</t>
+  </si>
+  <si>
+    <t>Assinatura Contrato</t>
+  </si>
+  <si>
+    <t>Recomendações AGU</t>
+  </si>
+  <si>
+    <t>Pré-Publicação</t>
+  </si>
+  <si>
+    <t>Montagem do Processo</t>
+  </si>
+  <si>
+    <t>Nota Técnica</t>
+  </si>
+  <si>
+    <t>AGU</t>
+  </si>
+  <si>
+    <t>Consolidação de Demanda</t>
+  </si>
+  <si>
+    <t>PE 90041/2024</t>
+  </si>
+  <si>
+    <t>PE 90040/2024</t>
+  </si>
+  <si>
+    <t>CC 90001/2024</t>
+  </si>
+  <si>
+    <t>PE 90038/2024</t>
+  </si>
+  <si>
+    <t>PE 90030/2024</t>
+  </si>
+  <si>
+    <t>TJDL 90001/2024</t>
+  </si>
+  <si>
+    <t>PE 90039/2024</t>
+  </si>
+  <si>
+    <t>PE 90022/2024</t>
+  </si>
+  <si>
+    <t>PE 90021/2024</t>
+  </si>
+  <si>
+    <t>PE 90008/2024</t>
+  </si>
+  <si>
+    <t>PE 90009/2024</t>
+  </si>
+  <si>
+    <t>PE 90005/2024</t>
+  </si>
+  <si>
+    <t>PE 90012/2024</t>
+  </si>
+  <si>
+    <t>PE 90017/2024</t>
+  </si>
+  <si>
+    <t>PE 90035/2024</t>
+  </si>
+  <si>
+    <t>PE 90007/2024</t>
+  </si>
+  <si>
+    <t>PE 90020/2024</t>
+  </si>
+  <si>
+    <t>PE 90023/2024</t>
+  </si>
+  <si>
+    <t>PE 90019/2024</t>
+  </si>
+  <si>
+    <t>PE 90002/2024</t>
+  </si>
+  <si>
+    <t>TJIL 90001/2024</t>
+  </si>
+  <si>
+    <t>PE 90044/2024</t>
+  </si>
+  <si>
+    <t>PE 90033/2024</t>
+  </si>
+  <si>
+    <t>PE 90031/2024</t>
+  </si>
+  <si>
+    <t>PE 90011/2024</t>
+  </si>
+  <si>
+    <t>PE 90016/2024</t>
+  </si>
+  <si>
+    <t>PE 90015/2024</t>
+  </si>
+  <si>
+    <t>PE 90025/2024</t>
+  </si>
+  <si>
+    <t>PE 90026/2024</t>
+  </si>
+  <si>
+    <t>PE 90036/2024</t>
+  </si>
+  <si>
+    <t>PE 90037/2024</t>
+  </si>
+  <si>
+    <t>PE 90027/2024</t>
+  </si>
+  <si>
+    <t>PE 90028/2024</t>
+  </si>
+  <si>
+    <t>PE 90006/2024</t>
+  </si>
+  <si>
+    <t>PE 13/2023</t>
+  </si>
+  <si>
+    <t>PE 08/2023</t>
+  </si>
+  <si>
+    <t>PE 07/2023</t>
+  </si>
+  <si>
+    <t>PE 90018/2024</t>
+  </si>
+  <si>
+    <t>PE 90013/2024</t>
+  </si>
+  <si>
+    <t>PE 90001/2024</t>
+  </si>
+  <si>
+    <t>PE 10/2023</t>
+  </si>
+  <si>
+    <t>PE 90014/2024</t>
+  </si>
+  <si>
+    <t>PE 90004/2024</t>
+  </si>
+  <si>
+    <t>PE 90029/2024</t>
+  </si>
+  <si>
+    <t>PE 90032/2024</t>
+  </si>
+  <si>
+    <t>PE 04/2023</t>
+  </si>
+  <si>
+    <t>PE 90010/2024</t>
+  </si>
+  <si>
+    <t>PE 90003/2024</t>
+  </si>
+  <si>
+    <t>PE 90024/2024</t>
+  </si>
+  <si>
+    <t>63402.001090/2024-29</t>
+  </si>
+  <si>
+    <t>63402.000915/2024-98</t>
+  </si>
+  <si>
+    <t>63402.000800/2024-01</t>
+  </si>
+  <si>
+    <t>63402.000881/2024-31</t>
+  </si>
+  <si>
+    <t>63402.000320/2024-32</t>
+  </si>
+  <si>
+    <t>63402.000403/2024-21</t>
+  </si>
+  <si>
+    <t>63402.000907/2024-41</t>
+  </si>
+  <si>
+    <t>63402.000357/2024-61</t>
+  </si>
+  <si>
+    <t>63402.000358/2024-13</t>
+  </si>
+  <si>
+    <t>63402.000318/2024-63</t>
+  </si>
+  <si>
+    <t>63402.000313/2024-31</t>
+  </si>
+  <si>
+    <t>63402.000330/2024-78</t>
+  </si>
+  <si>
+    <t>63402.000286/2024-04</t>
+  </si>
+  <si>
+    <t>63402.000317/2024-19</t>
+  </si>
+  <si>
+    <t>63402.000702/2024-66</t>
+  </si>
+  <si>
+    <t>63402.000331/2024-12</t>
+  </si>
+  <si>
+    <t>63402.000359/2024-50</t>
+  </si>
+  <si>
+    <t>63402.000355/2024-71</t>
+  </si>
+  <si>
+    <t>63402.000360/2024-84</t>
+  </si>
+  <si>
+    <t>63402.000338/2024-34</t>
+  </si>
+  <si>
+    <t>62055.000130/2024-40</t>
+  </si>
+  <si>
+    <t>63402.000327/2024-54</t>
+  </si>
+  <si>
+    <t>63402.000362/2024-73</t>
+  </si>
+  <si>
+    <t>63402.000332/2024-67</t>
+  </si>
+  <si>
+    <t>63402.000326/2024-18</t>
+  </si>
+  <si>
+    <t>63402.000319/2024-16</t>
+  </si>
+  <si>
+    <t>63402.000316/2024-74</t>
+  </si>
+  <si>
+    <t>63402.000361/2024-69</t>
+  </si>
+  <si>
+    <t>63402.000325/2024-65</t>
+  </si>
+  <si>
+    <t>63402.000750/2024-54</t>
+  </si>
+  <si>
+    <t>63402.000766/2024-67</t>
+  </si>
+  <si>
+    <t>63402.000324/2024-11</t>
+  </si>
+  <si>
+    <t>63402.000321/2024-87</t>
+  </si>
+  <si>
+    <t>63402.000328/2024-07</t>
+  </si>
+  <si>
+    <t>62055.002426/2023-14</t>
+  </si>
+  <si>
+    <t>62055.002424/2023-25</t>
+  </si>
+  <si>
+    <t>63402.000352/2024-38</t>
+  </si>
+  <si>
+    <t>63402.000289/2024-30</t>
+  </si>
+  <si>
+    <t>62055.002463/2023-22</t>
+  </si>
+  <si>
+    <t>63402.000315/2024-20</t>
+  </si>
+  <si>
+    <t>63402.000334/2024-56</t>
+  </si>
+  <si>
+    <t>63402.000333/2024-10</t>
+  </si>
+  <si>
+    <t>63402.000322/2024-21</t>
+  </si>
+  <si>
+    <t>62055.000344/2023-35</t>
+  </si>
+  <si>
+    <t>63402.000314/2024-85</t>
+  </si>
+  <si>
+    <t>63402.000312/2024-96</t>
+  </si>
+  <si>
+    <t>63402.000354/2024-27</t>
+  </si>
+  <si>
+    <t>Cestas Básicas</t>
+  </si>
+  <si>
+    <t>Concertina, portão e gradil</t>
+  </si>
+  <si>
+    <t>Nova Sede da CFB</t>
+  </si>
+  <si>
+    <t>Rede de Esgoto do GptFNB</t>
+  </si>
+  <si>
+    <t>Gêneros Secos</t>
+  </si>
+  <si>
+    <t>Agricultura Familiar</t>
+  </si>
+  <si>
+    <t>Manutenção de Elevadores</t>
+  </si>
+  <si>
+    <t>Mobiliários Corporativos</t>
+  </si>
+  <si>
+    <t>Serviços Gráficos Especializados</t>
+  </si>
+  <si>
+    <t>Material Permanente de Rancho</t>
+  </si>
+  <si>
+    <t>Moto Aquática</t>
+  </si>
+  <si>
+    <t>Provedor de Internet</t>
+  </si>
+  <si>
+    <t>Serviços de Ornamentação</t>
+  </si>
+  <si>
+    <t>Pisos e Revestimentos</t>
+  </si>
+  <si>
+    <t>Gestão de Frota</t>
+  </si>
+  <si>
+    <t>Água Mineral</t>
+  </si>
+  <si>
+    <t>Material Esportivo (PROFESP)</t>
+  </si>
+  <si>
+    <t>Periféricos de Informática</t>
+  </si>
+  <si>
+    <t>Material de Segurança Orgânica</t>
+  </si>
+  <si>
+    <t>Transporte de Carga</t>
+  </si>
+  <si>
+    <t>EBC</t>
+  </si>
+  <si>
+    <t>Serviços Comuns de Engenharia</t>
+  </si>
+  <si>
+    <t>Marinharia e Salvatagem</t>
+  </si>
+  <si>
+    <t>Gêneros Laticínios e Frios</t>
+  </si>
+  <si>
+    <t>Bebidas não-alcoólicas</t>
+  </si>
+  <si>
+    <t>Material para Copa e Cozinha</t>
+  </si>
+  <si>
+    <t>Material de Higiene e Limpeza</t>
+  </si>
+  <si>
+    <t>Material de Academia</t>
+  </si>
+  <si>
+    <t>Seguro de Viaturas</t>
+  </si>
+  <si>
+    <t>Jardinagem e Paisagismo</t>
+  </si>
+  <si>
+    <t>Transporte de Bagagem</t>
+  </si>
+  <si>
+    <t>Material Hidráulico</t>
+  </si>
+  <si>
+    <t>Gêneros Frigorificados</t>
+  </si>
+  <si>
+    <t>Telefonia Fixa</t>
+  </si>
+  <si>
+    <t>Material de Pintura</t>
+  </si>
+  <si>
+    <t>Panificados</t>
+  </si>
+  <si>
+    <t>Frigorificados – CFAT</t>
+  </si>
+  <si>
+    <t>Transporte de Pessoal</t>
+  </si>
+  <si>
+    <t>Montagem de Palanque</t>
+  </si>
+  <si>
+    <t>Gás Liquefeito de Petróleo (GLP)</t>
+  </si>
+  <si>
+    <t>Material Elétrico e Eletrônico</t>
+  </si>
+  <si>
+    <t>Material de Expediente</t>
+  </si>
+  <si>
+    <t>Gêneros Hortifrutigranjeiros</t>
+  </si>
+  <si>
+    <t>Equipamento de Informática</t>
+  </si>
+  <si>
+    <t>Material de Carpintaria</t>
+  </si>
+  <si>
+    <t>Material de Representação</t>
+  </si>
+  <si>
+    <t>Com7ºDN</t>
+  </si>
+  <si>
+    <t>ERMB</t>
+  </si>
+  <si>
+    <t>CFB</t>
+  </si>
+  <si>
+    <t>GptFNB</t>
+  </si>
+  <si>
+    <t>CeIMBra</t>
+  </si>
+  <si>
+    <t>CIAB</t>
+  </si>
+  <si>
+    <t>CFAT</t>
+  </si>
+  <si>
     <t>Centro de Intendência da Marinha em Brasília</t>
   </si>
   <si>
@@ -43,7 +520,7 @@
     <t>Controle de Dispensas Eletrônica</t>
   </si>
   <si>
-    <t>Atualizado em: 20/11/2024</t>
+    <t>Atualizado em: 21/11/2024</t>
   </si>
 </sst>
 </file>
@@ -91,12 +568,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -126,7 +615,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -139,6 +628,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,7 +929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -446,7 +941,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -456,7 +951,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>166</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -466,7 +961,7 @@
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>167</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -476,7 +971,7 @@
     </row>
     <row r="4" spans="1:6" ht="20" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -502,6 +997,986 @@
       </c>
       <c r="F5" s="4" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="6">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="6">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="5">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="6">
+        <v>14</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="5">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="6">
+        <v>16</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="5">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="6">
+        <v>18</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="5">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="6">
+        <v>20</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="5">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="6">
+        <v>22</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="5">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="6">
+        <v>24</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="5">
+        <v>25</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="6">
+        <v>26</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="5">
+        <v>27</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="6">
+        <v>28</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="5">
+        <v>29</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="6">
+        <v>30</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="5">
+        <v>31</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="6">
+        <v>32</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="5">
+        <v>33</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="6">
+        <v>34</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="5">
+        <v>35</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="6">
+        <v>36</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="5">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="6">
+        <v>38</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="5">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="6">
+        <v>40</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="5">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="6">
+        <v>42</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="5">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="6">
+        <v>44</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="5">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="6">
+        <v>46</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="5">
+        <v>47</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="6">
+        <v>48</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="5">
+        <v>49</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/tabela_resumida.xlsx
+++ b/tabela_resumida.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="175">
   <si>
     <t>Nº</t>
   </si>
@@ -43,456 +43,477 @@
     <t>Concluído</t>
   </si>
   <si>
-    <t>Assinatura Contrato</t>
-  </si>
-  <si>
-    <t>Recomendações AGU</t>
+    <t>Consolidação de Demanda</t>
   </si>
   <si>
     <t>Pré-Publicação</t>
   </si>
   <si>
+    <t>AGU</t>
+  </si>
+  <si>
+    <t>Nota Técnica</t>
+  </si>
+  <si>
+    <t>Atendimento da NT</t>
+  </si>
+  <si>
     <t>Montagem do Processo</t>
   </si>
   <si>
-    <t>Nota Técnica</t>
-  </si>
-  <si>
-    <t>AGU</t>
-  </si>
-  <si>
-    <t>Consolidação de Demanda</t>
+    <t>PE 90014/2024</t>
+  </si>
+  <si>
+    <t>PE 90016/2024</t>
+  </si>
+  <si>
+    <t>PE 90015/2024</t>
+  </si>
+  <si>
+    <t>PE 90004/2024</t>
+  </si>
+  <si>
+    <t>PE 90005/2024</t>
+  </si>
+  <si>
+    <t>PE 90006/2024</t>
+  </si>
+  <si>
+    <t>PE 90007/2024</t>
+  </si>
+  <si>
+    <t>PE 90009/2024</t>
+  </si>
+  <si>
+    <t>PE 90002/2024</t>
+  </si>
+  <si>
+    <t>PE 90003/2024</t>
+  </si>
+  <si>
+    <t>PE 90050/2024</t>
+  </si>
+  <si>
+    <t>PE 90049/2024</t>
   </si>
   <si>
     <t>PE 90041/2024</t>
   </si>
   <si>
+    <t>PE 90038/2024</t>
+  </si>
+  <si>
+    <t>PE 90037/2024</t>
+  </si>
+  <si>
+    <t>PE 90035/2024</t>
+  </si>
+  <si>
+    <t>TJIL 90001/2024</t>
+  </si>
+  <si>
+    <t>PE 90044/2024</t>
+  </si>
+  <si>
+    <t>PE 90033/2024</t>
+  </si>
+  <si>
+    <t>PE 90029/2024</t>
+  </si>
+  <si>
+    <t>PE 90026/2024</t>
+  </si>
+  <si>
+    <t>PE 90025/2024</t>
+  </si>
+  <si>
+    <t>PE 90023/2024</t>
+  </si>
+  <si>
+    <t>PE 90022/2024</t>
+  </si>
+  <si>
+    <t>PE 90021/2024</t>
+  </si>
+  <si>
+    <t>PE 90018/2024</t>
+  </si>
+  <si>
+    <t>PE 90017/2024</t>
+  </si>
+  <si>
+    <t>PE 90060/2024</t>
+  </si>
+  <si>
+    <t>PE 90052/2024</t>
+  </si>
+  <si>
+    <t>PE 90053/2024</t>
+  </si>
+  <si>
+    <t>PE 90054/2024</t>
+  </si>
+  <si>
+    <t>PE 90056/2024</t>
+  </si>
+  <si>
+    <t>PE 90057/2024</t>
+  </si>
+  <si>
+    <t>PE 90058/2024</t>
+  </si>
+  <si>
+    <t>PE 90059/2024</t>
+  </si>
+  <si>
+    <t>PE 90064/2024</t>
+  </si>
+  <si>
+    <t>PE 90061/2024</t>
+  </si>
+  <si>
+    <t>PE 90062/2024</t>
+  </si>
+  <si>
+    <t>PE 90063/2024</t>
+  </si>
+  <si>
+    <t>PE 90065/2024</t>
+  </si>
+  <si>
+    <t>PE 90012/2024</t>
+  </si>
+  <si>
+    <t>PE 90020/2024</t>
+  </si>
+  <si>
+    <t>PE 90024/2024</t>
+  </si>
+  <si>
+    <t>PE 90013/2024</t>
+  </si>
+  <si>
+    <t>PE 90010/2024</t>
+  </si>
+  <si>
+    <t>CC 90001/2024</t>
+  </si>
+  <si>
+    <t>PE 90008/2024</t>
+  </si>
+  <si>
     <t>PE 90040/2024</t>
   </si>
   <si>
-    <t>CC 90001/2024</t>
-  </si>
-  <si>
-    <t>PE 90038/2024</t>
+    <t>PE 90036/2024</t>
+  </si>
+  <si>
+    <t>PE 90031/2024</t>
+  </si>
+  <si>
+    <t>TJDL 90001/2024</t>
+  </si>
+  <si>
+    <t>PE 90019/2024</t>
+  </si>
+  <si>
+    <t>PE 90028/2024</t>
+  </si>
+  <si>
+    <t>PE 90039/2024</t>
+  </si>
+  <si>
+    <t>PE 90001/2024</t>
+  </si>
+  <si>
+    <t>PE 90011/2024</t>
+  </si>
+  <si>
+    <t>PE 90027/2024</t>
   </si>
   <si>
     <t>PE 90030/2024</t>
   </si>
   <si>
-    <t>TJDL 90001/2024</t>
-  </si>
-  <si>
-    <t>PE 90039/2024</t>
-  </si>
-  <si>
-    <t>PE 90022/2024</t>
-  </si>
-  <si>
-    <t>PE 90021/2024</t>
-  </si>
-  <si>
-    <t>PE 90008/2024</t>
-  </si>
-  <si>
-    <t>PE 90009/2024</t>
-  </si>
-  <si>
-    <t>PE 90005/2024</t>
-  </si>
-  <si>
-    <t>PE 90012/2024</t>
-  </si>
-  <si>
-    <t>PE 90017/2024</t>
-  </si>
-  <si>
-    <t>PE 90035/2024</t>
-  </si>
-  <si>
-    <t>PE 90007/2024</t>
-  </si>
-  <si>
-    <t>PE 90020/2024</t>
-  </si>
-  <si>
-    <t>PE 90023/2024</t>
-  </si>
-  <si>
-    <t>PE 90019/2024</t>
-  </si>
-  <si>
-    <t>PE 90002/2024</t>
-  </si>
-  <si>
-    <t>TJIL 90001/2024</t>
-  </si>
-  <si>
-    <t>PE 90044/2024</t>
-  </si>
-  <si>
-    <t>PE 90033/2024</t>
-  </si>
-  <si>
-    <t>PE 90031/2024</t>
-  </si>
-  <si>
-    <t>PE 90011/2024</t>
-  </si>
-  <si>
-    <t>PE 90016/2024</t>
-  </si>
-  <si>
-    <t>PE 90015/2024</t>
-  </si>
-  <si>
-    <t>PE 90025/2024</t>
-  </si>
-  <si>
-    <t>PE 90026/2024</t>
-  </si>
-  <si>
-    <t>PE 90036/2024</t>
-  </si>
-  <si>
-    <t>PE 90037/2024</t>
-  </si>
-  <si>
-    <t>PE 90027/2024</t>
-  </si>
-  <si>
-    <t>PE 90028/2024</t>
-  </si>
-  <si>
-    <t>PE 90006/2024</t>
-  </si>
-  <si>
-    <t>PE 13/2023</t>
-  </si>
-  <si>
-    <t>PE 08/2023</t>
-  </si>
-  <si>
-    <t>PE 07/2023</t>
-  </si>
-  <si>
-    <t>PE 90018/2024</t>
-  </si>
-  <si>
-    <t>PE 90013/2024</t>
-  </si>
-  <si>
-    <t>PE 90001/2024</t>
-  </si>
-  <si>
-    <t>PE 10/2023</t>
-  </si>
-  <si>
-    <t>PE 90014/2024</t>
-  </si>
-  <si>
-    <t>PE 90004/2024</t>
-  </si>
-  <si>
-    <t>PE 90029/2024</t>
-  </si>
-  <si>
     <t>PE 90032/2024</t>
   </si>
   <si>
-    <t>PE 04/2023</t>
-  </si>
-  <si>
-    <t>PE 90010/2024</t>
-  </si>
-  <si>
-    <t>PE 90003/2024</t>
-  </si>
-  <si>
-    <t>PE 90024/2024</t>
+    <t>63402.000315/2024-20</t>
+  </si>
+  <si>
+    <t>63402.000319/2024-16</t>
+  </si>
+  <si>
+    <t>63402.000316/2024-74</t>
+  </si>
+  <si>
+    <t>63402.000334/2024-56</t>
+  </si>
+  <si>
+    <t>63402.000330/2024-78</t>
+  </si>
+  <si>
+    <t>63402.000328/2024-07</t>
+  </si>
+  <si>
+    <t>63402.000331/2024-12</t>
+  </si>
+  <si>
+    <t>63402.000313/2024-31</t>
+  </si>
+  <si>
+    <t>63402.000338/2024-34</t>
+  </si>
+  <si>
+    <t>63402.000312/2024-96</t>
+  </si>
+  <si>
+    <t>X</t>
   </si>
   <si>
     <t>63402.001090/2024-29</t>
   </si>
   <si>
+    <t>63402.000881/2024-31</t>
+  </si>
+  <si>
+    <t>63402.000766/2024-67</t>
+  </si>
+  <si>
+    <t>63402.000702/2024-66</t>
+  </si>
+  <si>
+    <t>62055.000130/2024-40</t>
+  </si>
+  <si>
+    <t>63402.000327/2024-54</t>
+  </si>
+  <si>
+    <t>63402.000362/2024-73</t>
+  </si>
+  <si>
+    <t>63402.000333/2024-10</t>
+  </si>
+  <si>
+    <t>63402.000325/2024-65</t>
+  </si>
+  <si>
+    <t>63402.000361/2024-69</t>
+  </si>
+  <si>
+    <t>63402.000355/2024-71</t>
+  </si>
+  <si>
+    <t>63402.000357/2024-61</t>
+  </si>
+  <si>
+    <t>63402.000358/2024-13</t>
+  </si>
+  <si>
+    <t>63402.000352/2024-38</t>
+  </si>
+  <si>
+    <t>63402.000317/2024-19</t>
+  </si>
+  <si>
+    <t>63402.000289/2024-30</t>
+  </si>
+  <si>
+    <t>63402.000360/2024-84</t>
+  </si>
+  <si>
+    <t>63402.000332/2024-67</t>
+  </si>
+  <si>
+    <t>63402.000318/2024-63</t>
+  </si>
+  <si>
+    <t>63402.000321/2024-87</t>
+  </si>
+  <si>
+    <t>63402.000286/2024-04</t>
+  </si>
+  <si>
+    <t>63402.000359/2024-50</t>
+  </si>
+  <si>
+    <t>63402.000354/2024-27</t>
+  </si>
+  <si>
+    <t>63402.000314/2024-85</t>
+  </si>
+  <si>
+    <t>63402.000800/2024-01</t>
+  </si>
+  <si>
     <t>63402.000915/2024-98</t>
   </si>
   <si>
-    <t>63402.000800/2024-01</t>
-  </si>
-  <si>
-    <t>63402.000881/2024-31</t>
+    <t>63402.000750/2024-54</t>
+  </si>
+  <si>
+    <t>63402.000403/2024-21</t>
+  </si>
+  <si>
+    <t>63402.000907/2024-41</t>
+  </si>
+  <si>
+    <t>62055.002463/2023-22</t>
+  </si>
+  <si>
+    <t>63402.000326/2024-18</t>
+  </si>
+  <si>
+    <t>63402.000324/2024-11</t>
   </si>
   <si>
     <t>63402.000320/2024-32</t>
   </si>
   <si>
-    <t>63402.000403/2024-21</t>
-  </si>
-  <si>
-    <t>63402.000907/2024-41</t>
-  </si>
-  <si>
-    <t>63402.000357/2024-61</t>
-  </si>
-  <si>
-    <t>63402.000358/2024-13</t>
-  </si>
-  <si>
-    <t>63402.000318/2024-63</t>
-  </si>
-  <si>
-    <t>63402.000313/2024-31</t>
-  </si>
-  <si>
-    <t>63402.000330/2024-78</t>
-  </si>
-  <si>
-    <t>63402.000286/2024-04</t>
-  </si>
-  <si>
-    <t>63402.000317/2024-19</t>
-  </si>
-  <si>
-    <t>63402.000702/2024-66</t>
-  </si>
-  <si>
-    <t>63402.000331/2024-12</t>
-  </si>
-  <si>
-    <t>63402.000359/2024-50</t>
-  </si>
-  <si>
-    <t>63402.000355/2024-71</t>
-  </si>
-  <si>
-    <t>63402.000360/2024-84</t>
-  </si>
-  <si>
-    <t>63402.000338/2024-34</t>
-  </si>
-  <si>
-    <t>62055.000130/2024-40</t>
-  </si>
-  <si>
-    <t>63402.000327/2024-54</t>
-  </si>
-  <si>
-    <t>63402.000362/2024-73</t>
-  </si>
-  <si>
-    <t>63402.000332/2024-67</t>
-  </si>
-  <si>
-    <t>63402.000326/2024-18</t>
-  </si>
-  <si>
-    <t>63402.000319/2024-16</t>
-  </si>
-  <si>
-    <t>63402.000316/2024-74</t>
-  </si>
-  <si>
-    <t>63402.000361/2024-69</t>
-  </si>
-  <si>
-    <t>63402.000325/2024-65</t>
-  </si>
-  <si>
-    <t>63402.000750/2024-54</t>
-  </si>
-  <si>
-    <t>63402.000766/2024-67</t>
-  </si>
-  <si>
-    <t>63402.000324/2024-11</t>
-  </si>
-  <si>
-    <t>63402.000321/2024-87</t>
-  </si>
-  <si>
-    <t>63402.000328/2024-07</t>
-  </si>
-  <si>
-    <t>62055.002426/2023-14</t>
-  </si>
-  <si>
-    <t>62055.002424/2023-25</t>
-  </si>
-  <si>
-    <t>63402.000352/2024-38</t>
-  </si>
-  <si>
-    <t>63402.000289/2024-30</t>
-  </si>
-  <si>
-    <t>62055.002463/2023-22</t>
-  </si>
-  <si>
-    <t>63402.000315/2024-20</t>
-  </si>
-  <si>
-    <t>63402.000334/2024-56</t>
-  </si>
-  <si>
-    <t>63402.000333/2024-10</t>
-  </si>
-  <si>
     <t>63402.000322/2024-21</t>
   </si>
   <si>
-    <t>62055.000344/2023-35</t>
-  </si>
-  <si>
-    <t>63402.000314/2024-85</t>
-  </si>
-  <si>
-    <t>63402.000312/2024-96</t>
-  </si>
-  <si>
-    <t>63402.000354/2024-27</t>
+    <t>Material de Expediente</t>
+  </si>
+  <si>
+    <t>Material para Copa e Cozinha</t>
+  </si>
+  <si>
+    <t>Material de Higiene e Limpeza</t>
   </si>
   <si>
     <t>Cestas Básicas</t>
   </si>
   <si>
+    <t>Provedor de Internet</t>
+  </si>
+  <si>
+    <t>Telefonia Fixa</t>
+  </si>
+  <si>
+    <t>Água Mineral</t>
+  </si>
+  <si>
+    <t>Moto Aquática</t>
+  </si>
+  <si>
+    <t>Transporte de Carga</t>
+  </si>
+  <si>
+    <t>Manutenção de Elevadores</t>
+  </si>
+  <si>
+    <t>TESTE</t>
+  </si>
+  <si>
+    <t>Rede de Esgoto do GptFNB</t>
+  </si>
+  <si>
+    <t>Transporte de Bagagem</t>
+  </si>
+  <si>
+    <t>(Renumerado 1/2025) Gestão de Frota</t>
+  </si>
+  <si>
+    <t>EBC</t>
+  </si>
+  <si>
+    <t>Serviços Comuns de Engenharia</t>
+  </si>
+  <si>
+    <t>Marinharia e Salvatagem</t>
+  </si>
+  <si>
+    <t>Gêneros Hortifrutigranjeiros</t>
+  </si>
+  <si>
+    <t>Seguro de Viaturas</t>
+  </si>
+  <si>
+    <t>Material de Academia</t>
+  </si>
+  <si>
+    <t>Periféricos de Informática</t>
+  </si>
+  <si>
+    <t>Mobiliários Corporativos</t>
+  </si>
+  <si>
+    <t>Serviços Gráficos Especializados</t>
+  </si>
+  <si>
+    <t>Transporte de Pessoal</t>
+  </si>
+  <si>
+    <t>Pisos e Revestimentos</t>
+  </si>
+  <si>
+    <t>Montagem de Palanque</t>
+  </si>
+  <si>
+    <t>Material de Segurança Orgânica</t>
+  </si>
+  <si>
+    <t>Gêneros Laticínios e Frios</t>
+  </si>
+  <si>
+    <t>Material Permanente de Rancho</t>
+  </si>
+  <si>
+    <t>Gêneros Frigorificados</t>
+  </si>
+  <si>
+    <t>Serviços de Ornamentação</t>
+  </si>
+  <si>
+    <t>Material Esportivo (PROFESP)</t>
+  </si>
+  <si>
+    <t>Material de Representação</t>
+  </si>
+  <si>
+    <t>Material de Carpintaria</t>
+  </si>
+  <si>
+    <t>Nova Sede da CFB</t>
+  </si>
+  <si>
+    <t>(Renumerado 90066/2024) Material Permanente de Rancho</t>
+  </si>
+  <si>
     <t>Concertina, portão e gradil</t>
   </si>
   <si>
-    <t>Nova Sede da CFB</t>
-  </si>
-  <si>
-    <t>Rede de Esgoto do GptFNB</t>
+    <t>Jardinagem e Paisagismo</t>
+  </si>
+  <si>
+    <t>Agricultura Familiar</t>
+  </si>
+  <si>
+    <t>(Renumerado 90065/2024) Gêneros Frigorificados</t>
+  </si>
+  <si>
+    <t>(Renumerado 90066/2024) Gás Liquefeito de Petróleo (GLP)</t>
+  </si>
+  <si>
+    <t>Bebidas não-alcoólicas</t>
+  </si>
+  <si>
+    <t>Material Hidráulico</t>
   </si>
   <si>
     <t>Gêneros Secos</t>
   </si>
   <si>
-    <t>Agricultura Familiar</t>
-  </si>
-  <si>
-    <t>Manutenção de Elevadores</t>
-  </si>
-  <si>
-    <t>Mobiliários Corporativos</t>
-  </si>
-  <si>
-    <t>Serviços Gráficos Especializados</t>
-  </si>
-  <si>
-    <t>Material Permanente de Rancho</t>
-  </si>
-  <si>
-    <t>Moto Aquática</t>
-  </si>
-  <si>
-    <t>Provedor de Internet</t>
-  </si>
-  <si>
-    <t>Serviços de Ornamentação</t>
-  </si>
-  <si>
-    <t>Pisos e Revestimentos</t>
-  </si>
-  <si>
-    <t>Gestão de Frota</t>
-  </si>
-  <si>
-    <t>Água Mineral</t>
-  </si>
-  <si>
-    <t>Material Esportivo (PROFESP)</t>
-  </si>
-  <si>
-    <t>Periféricos de Informática</t>
-  </si>
-  <si>
-    <t>Material de Segurança Orgânica</t>
-  </si>
-  <si>
-    <t>Transporte de Carga</t>
-  </si>
-  <si>
-    <t>EBC</t>
-  </si>
-  <si>
-    <t>Serviços Comuns de Engenharia</t>
-  </si>
-  <si>
-    <t>Marinharia e Salvatagem</t>
-  </si>
-  <si>
-    <t>Gêneros Laticínios e Frios</t>
-  </si>
-  <si>
-    <t>Bebidas não-alcoólicas</t>
-  </si>
-  <si>
-    <t>Material para Copa e Cozinha</t>
-  </si>
-  <si>
-    <t>Material de Higiene e Limpeza</t>
-  </si>
-  <si>
-    <t>Material de Academia</t>
-  </si>
-  <si>
-    <t>Seguro de Viaturas</t>
-  </si>
-  <si>
-    <t>Jardinagem e Paisagismo</t>
-  </si>
-  <si>
-    <t>Transporte de Bagagem</t>
-  </si>
-  <si>
-    <t>Material Hidráulico</t>
-  </si>
-  <si>
-    <t>Gêneros Frigorificados</t>
-  </si>
-  <si>
-    <t>Telefonia Fixa</t>
-  </si>
-  <si>
-    <t>Material de Pintura</t>
-  </si>
-  <si>
-    <t>Panificados</t>
-  </si>
-  <si>
-    <t>Frigorificados – CFAT</t>
-  </si>
-  <si>
-    <t>Transporte de Pessoal</t>
-  </si>
-  <si>
-    <t>Montagem de Palanque</t>
-  </si>
-  <si>
-    <t>Gás Liquefeito de Petróleo (GLP)</t>
-  </si>
-  <si>
-    <t>Material Elétrico e Eletrônico</t>
-  </si>
-  <si>
-    <t>Material de Expediente</t>
-  </si>
-  <si>
-    <t>Gêneros Hortifrutigranjeiros</t>
-  </si>
-  <si>
     <t>Equipamento de Informática</t>
   </si>
   <si>
-    <t>Material de Carpintaria</t>
-  </si>
-  <si>
-    <t>Material de Representação</t>
-  </si>
-  <si>
     <t>Com7ºDN</t>
   </si>
   <si>
+    <t>CeIMBra</t>
+  </si>
+  <si>
     <t>ERMB</t>
   </si>
   <si>
@@ -502,15 +523,12 @@
     <t>GptFNB</t>
   </si>
   <si>
-    <t>CeIMBra</t>
+    <t>CFAT</t>
   </si>
   <si>
     <t>CIAB</t>
   </si>
   <si>
-    <t>CFAT</t>
-  </si>
-  <si>
     <t>Centro de Intendência da Marinha em Brasília</t>
   </si>
   <si>
@@ -520,7 +538,7 @@
     <t>Controle de Dispensas Eletrônica</t>
   </si>
   <si>
-    <t>Atualizado em: 21/11/2024</t>
+    <t>Atualizado em: 25/11/2024</t>
   </si>
 </sst>
 </file>
@@ -929,7 +947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -941,7 +959,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -951,7 +969,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -961,7 +979,7 @@
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -971,7 +989,7 @@
     </row>
     <row r="4" spans="1:6" ht="20" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1007,16 +1025,16 @@
         <v>6</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1027,16 +1045,16 @@
         <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1047,16 +1065,16 @@
         <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1067,16 +1085,16 @@
         <v>6</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1087,16 +1105,16 @@
         <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1107,16 +1125,16 @@
         <v>6</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1127,16 +1145,16 @@
         <v>6</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1144,19 +1162,19 @@
         <v>8</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1164,19 +1182,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1184,19 +1202,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1204,19 +1222,15 @@
         <v>11</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>122</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1224,19 +1238,19 @@
         <v>12</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1244,19 +1258,19 @@
         <v>13</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1264,19 +1278,19 @@
         <v>14</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1284,19 +1298,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1304,19 +1318,19 @@
         <v>16</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1324,19 +1338,19 @@
         <v>17</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1344,19 +1358,19 @@
         <v>18</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1364,19 +1378,19 @@
         <v>19</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1384,19 +1398,19 @@
         <v>20</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1404,19 +1418,19 @@
         <v>21</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1424,16 +1438,16 @@
         <v>22</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>164</v>
@@ -1444,19 +1458,19 @@
         <v>23</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1464,19 +1478,19 @@
         <v>24</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1484,19 +1498,19 @@
         <v>25</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1504,19 +1518,19 @@
         <v>26</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1524,19 +1538,19 @@
         <v>27</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1544,19 +1558,19 @@
         <v>28</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1564,19 +1578,19 @@
         <v>29</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1584,19 +1598,19 @@
         <v>30</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1604,19 +1618,19 @@
         <v>31</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1624,19 +1638,19 @@
         <v>32</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1644,19 +1658,19 @@
         <v>33</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1664,19 +1678,19 @@
         <v>34</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1684,19 +1698,19 @@
         <v>35</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1704,19 +1718,19 @@
         <v>36</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1724,16 +1738,16 @@
         <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>164</v>
@@ -1744,19 +1758,19 @@
         <v>38</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1764,19 +1778,19 @@
         <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1784,19 +1798,19 @@
         <v>40</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1804,19 +1818,19 @@
         <v>41</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1824,19 +1838,19 @@
         <v>42</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1844,19 +1858,19 @@
         <v>43</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1864,19 +1878,19 @@
         <v>44</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1884,19 +1898,19 @@
         <v>45</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -1904,19 +1918,19 @@
         <v>46</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1924,19 +1938,19 @@
         <v>47</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1944,19 +1958,19 @@
         <v>48</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>110</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -1964,19 +1978,219 @@
         <v>49</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>111</v>
       </c>
       <c r="E54" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="6">
+        <v>50</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="5">
+        <v>51</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E56" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="F54" s="5" t="s">
+      <c r="F56" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="6">
+        <v>52</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="5">
+        <v>53</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E58" s="5" t="s">
         <v>158</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="6">
+        <v>54</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="5">
+        <v>55</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="6">
+        <v>56</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="5">
+        <v>57</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="6">
+        <v>58</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="5">
+        <v>59</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
